--- a/documents/Change_Log.xlsx
+++ b/documents/Change_Log.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suman\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Shafiq_Pagoole\Projects\pagoole_discount_shop\Git\pagoole-discount-shop\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2F17F6-3B7D-406D-A984-CCF3775FE3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12315"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="592" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Change_Request" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="93">
   <si>
     <t>SL</t>
   </si>
@@ -131,28 +132,184 @@
     <t>Shop Admin Can't see the product list. (After copmleting this other can be tested)</t>
   </si>
   <si>
-    <t>DB (Done)</t>
-  </si>
-  <si>
-    <t>DB(No issue)</t>
-  </si>
-  <si>
-    <t>App(No issue)</t>
-  </si>
-  <si>
-    <t>DB(Done)</t>
-  </si>
-  <si>
-    <t>App(Done)</t>
-  </si>
-  <si>
-    <t>App(DOne)</t>
+    <t>discount_shop.VENDOR_PRODUCTS</t>
+  </si>
+  <si>
+    <t>Add new column DESCRIPTION (1000), Admin will select the description form vendore description list and the main product desctiption column will be updated. Admin will update raw html text format.</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>App Mobile View</t>
+  </si>
+  <si>
+    <t>In deskto view by default the category panel will display but in Mobile view by default category list will not show, if user click on menu then the list will show.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location Selection </t>
+  </si>
+  <si>
+    <t>Product Details Page Seller List</t>
+  </si>
+  <si>
+    <t>When product product details page will be visited from any specific vendore then the vendor will show in &lt;&gt;This Shop&lt;/&gt; header and then will show in &lt;&gt;Others Shop&lt;/&gt; seller list.</t>
+  </si>
+  <si>
+    <t>Admin + Shop_Admin</t>
+  </si>
+  <si>
+    <t>Product History (Purchase, Delivery, Customer Return, and Suppliers Return)</t>
+  </si>
+  <si>
+    <t>Product Stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamic Location Parent Selection Function (Example Shown In Apex), The number of parent will picked from APPLICATION_CONFIGURATION table and item name will be LOCATION_PARENT_TO_DISPLAY. If no parent data is found then by default will display 3 parent, including the current total 4. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add a new column PURCHASE_PRICE data type NUMBER (12, 2) </t>
+  </si>
+  <si>
+    <t>Vendor Can See the product stock details. And total stock quentity of products list and amount based on the purchase price.</t>
+  </si>
+  <si>
+    <t>Vendor can create new invoice using any mobile number. (In this case if user not exist then user will be created similar to login with OTP process).</t>
+  </si>
+  <si>
+    <t>Invoice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop admin can add multiple seller for his/her shop. (Search Pagoole user by email or mobile or Name and one request will be generated to the pagoole user and if user accept this from the notification then the user can act as a sales man of this shop) </t>
+  </si>
+  <si>
+    <t>Shop_Sales_Person</t>
+  </si>
+  <si>
+    <t>Can create invoice and can see his/her sales record and day order can be updated by the user if not completed by the Shop_Admin</t>
+  </si>
+  <si>
+    <t>Shop_Admin will accept all sales of a Shop_Sales_Person sales record on by one or using select check box.</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Login With Google, Pagoole, Login With OTP. (All will be configurable to Application Configuration LOGIN_WITH_GOOGLE, LOGIN_WITH_OTP value will be true/false default value will be false if not exist)</t>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>Application API</t>
+  </si>
+  <si>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>Error handle all API's if not exist or error the application not run.</t>
+  </si>
+  <si>
+    <t>Shop_Admin / Shop_Sales_Person</t>
+  </si>
+  <si>
+    <t>Vendor can create new invoice using any mobile number. (In this case if user not exist then user will be created similar to login with OTP process). :: In that case one email will be generated to this customer. (Order Confirmation) Email template will be configurable from table, New Table Added for Email Configuration.</t>
+  </si>
+  <si>
+    <t>Send Email API</t>
+  </si>
+  <si>
+    <t>discount_shop.EMAIL_TEMPLATES</t>
+  </si>
+  <si>
+    <t>Email Sending API.</t>
+  </si>
+  <si>
+    <t>discount_shop.EMAIL_LOG</t>
+  </si>
+  <si>
+    <t>Email Template Configuration. Please See the database script.</t>
+  </si>
+  <si>
+    <t>Email History. Please See the database script.</t>
+  </si>
+  <si>
+    <t>Help And Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User Help and support icon add to header / footer and url will be automatically captured and stored for help and support </t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Add App List (9 dot) button app list from our main site to the top right before my profile picture. And will show the app list simila to Pagoole app list.</t>
+  </si>
+  <si>
+    <t>Add App logo Pagoole (Multicolor) and simiar to paggole account. (Pagoole Discount Shop)</t>
+  </si>
+  <si>
+    <t>Correct the discount shop footer.</t>
+  </si>
+  <si>
+    <t>Set all table name case insencetive for database SQL queris.</t>
+  </si>
+  <si>
+    <t>Correct the favicon icon from pagoole.com</t>
+  </si>
+  <si>
+    <t>https://www.bazarsuru.com/product/japanese-sk5-stainless-steel-multi-function-kitchen-scissors/</t>
+  </si>
+  <si>
+    <t>Search text box and Shop Order button positioning in Mobile View. Example (https://www.bazarsuru.com/product/japanese-sk5-stainless-steel-multi-function-kitchen-scissors/)</t>
+  </si>
+  <si>
+    <t>Add Shop Whatts App / Mobile Number to Product Details Page Seller List. So that user can directly contact with seller via whatts app.</t>
+  </si>
+  <si>
+    <t>Invoice History Sales Including Sales Persons informations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shop admin can </t>
+  </si>
+  <si>
+    <t>discount_shop.Vendors</t>
+  </si>
+  <si>
+    <t>Apply store name column unique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOGIN With Pagoole, Return Userid also, currently returning email or mobile. </t>
+  </si>
+  <si>
+    <t>Categiry Pannel Will Not Be Scroll.</t>
+  </si>
+  <si>
+    <t>Login With OTP</t>
+  </si>
+  <si>
+    <t>Login With Google.</t>
+  </si>
+  <si>
+    <t>Category Design Issue ass discussed.</t>
+  </si>
+  <si>
+    <t>In Navigation Bar Pagoole color will be same as https://account.pagoole.com/ -- And will be Pagoole Discount Shop</t>
+  </si>
+  <si>
+    <t>Nabbar will be same in all over discountshop. User Profile Menu and Application List Button will be same as https://account.pagoole.com/. (And Same Applist Will Show) and all colors will be same.</t>
+  </si>
+  <si>
+    <t>Shop Order Iconic Button add in right side menu icon. And another description div in bottom part of Shop List (After Redirection of Shop Order Button / Shop List)</t>
+  </si>
+  <si>
+    <t>Shafiqul</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -185,7 +342,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -198,8 +355,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -222,23 +391,75 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -255,60 +476,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1895475</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="184731" cy="264560"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4533900" y="1304925"/>
-          <a:ext cx="184731" cy="264560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -573,286 +740,1435 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J134"/>
+  <sheetFormatPr defaultColWidth="40.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="160" customWidth="1"/>
-    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" customWidth="1"/>
+    <col min="6" max="6" width="55.7109375" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="139.85546875" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="B6" s="5">
         <v>45947</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5">
+        <v>45947</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10">
+        <v>45947</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="9"/>
+      <c r="H12" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>13</v>
+      </c>
+      <c r="B15" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>15</v>
+      </c>
+      <c r="B17" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>16</v>
+      </c>
+      <c r="B18" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>17</v>
+      </c>
+      <c r="B19" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>18</v>
+      </c>
+      <c r="B20" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>19</v>
+      </c>
+      <c r="B21" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F21" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>20</v>
+      </c>
+      <c r="B22" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>21</v>
+      </c>
+      <c r="B23" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>22</v>
+      </c>
+      <c r="B24" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>23</v>
+      </c>
+      <c r="B25" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>24</v>
+      </c>
+      <c r="B26" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>25</v>
+      </c>
+      <c r="B27" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
         <v>26</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3" t="s">
+      <c r="B28" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="4"/>
+      <c r="H28" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>27</v>
+      </c>
+      <c r="B29" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>28</v>
+      </c>
+      <c r="B30" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>29</v>
+      </c>
+      <c r="B31" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3">
-        <v>45947</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B32" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>31</v>
+      </c>
+      <c r="B33" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>32</v>
+      </c>
+      <c r="B34" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>33</v>
+      </c>
+      <c r="B35" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>34</v>
+      </c>
+      <c r="B36" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>35</v>
+      </c>
+      <c r="B37" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>36</v>
+      </c>
+      <c r="B38" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>37</v>
+      </c>
+      <c r="B39" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>38</v>
+      </c>
+      <c r="B40" s="12">
+        <v>45964</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="18">
         <v>39</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
-        <v>45947</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3">
-        <v>45947</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3">
-        <v>45947</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3">
-        <v>45947</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B41" s="19">
+        <v>45970</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3">
-        <v>45947</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3">
-        <v>45947</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3">
-        <v>45947</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D41" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H41" s="21"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
         <v>40</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3">
-        <v>45947</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>9</v>
-      </c>
-      <c r="B12" s="8">
-        <v>45947</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="B42" s="12">
+        <v>45970</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>34</v>
+      <c r="F42" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>41</v>
+      </c>
+      <c r="B43" s="12">
+        <v>45970</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>42</v>
+      </c>
+      <c r="B44" s="12">
+        <v>45970</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>42</v>
+      </c>
+      <c r="B45" s="12">
+        <v>45970</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>42</v>
+      </c>
+      <c r="B46" s="12">
+        <v>45970</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>42</v>
+      </c>
+      <c r="B47" s="12">
+        <v>45970</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>42</v>
+      </c>
+      <c r="B48" s="12">
+        <v>45970</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="4">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="4">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="4">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="4">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="4">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="4">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="4">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="4">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="4">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="4">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="4">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="4">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="4">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="4">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="4">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="4">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="4">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="4">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="4">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F8" r:id="rId1"/>
-    <hyperlink ref="F9" r:id="rId2"/>
-    <hyperlink ref="F3" r:id="rId3"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{14048393-5298-491A-A6CB-832349813831}"/>
+    <hyperlink ref="G9" r:id="rId2" xr:uid="{F74CEE51-424B-4B96-85D2-FBE61E3A0A39}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{1323A88F-9455-4CEC-8F54-B442B7DDC9A8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
 </worksheet>
 </file>